--- a/automotive_forms/017_quick_release_steering_wheel_installation_checklist--automotive_forms.xlsx
+++ b/automotive_forms/017_quick_release_steering_wheel_installation_checklist--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>certified_preowned</t>
+          <t>certified preowned</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quick_release</t>
+          <t>quick release</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>power_locking</t>
+          <t>power locking</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bolt_on</t>
+          <t>bolt on</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>press_fit</t>
+          <t>press fit</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>snap_on</t>
+          <t>snap on</t>
         </is>
       </c>
     </row>
